--- a/Statistics/Section 2 - Descriptive Statistics Fundamentals/1_Types of data and levels of measurement/Glossary.xlsx
+++ b/Statistics/Section 2 - Descriptive Statistics Fundamentals/1_Types of data and levels of measurement/Glossary.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\slong\365 Data Science\Statistics\Section 2 - Descriptive Statistics Fundamentals\1_Types of data and levels of measurement\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{863F052D-7062-4A29-9532-20C8F9CFC623}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A9441125-80A3-4B5C-ACE5-43C6DBA1E63D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="30936" windowHeight="16776" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -1330,7 +1330,7 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="9" x14ac:knownFonts="1">
+  <fonts count="8" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -1350,13 +1350,6 @@
       <color rgb="FF002060"/>
       <name val="Arial"/>
       <family val="2"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color theme="1"/>
-      <name val="Calibri"/>
-      <family val="2"/>
-      <scheme val="minor"/>
     </font>
     <font>
       <sz val="11"/>
@@ -1478,8 +1471,8 @@
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="4" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="5" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
@@ -1492,7 +1485,7 @@
     <xf numFmtId="0" fontId="0" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="6" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -1819,7 +1812,7 @@
   <sheetFormatPr defaultRowHeight="11.4" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="2" style="1" customWidth="1"/>
-    <col min="2" max="2" width="7" style="1" customWidth="1"/>
+    <col min="2" max="2" width="8.77734375" style="1" customWidth="1"/>
     <col min="3" max="3" width="42.6640625" style="1" customWidth="1"/>
     <col min="4" max="4" width="28.21875" style="1" customWidth="1"/>
     <col min="5" max="5" width="77.6640625" style="1" customWidth="1"/>
@@ -2510,7 +2503,7 @@
         <v>84</v>
       </c>
     </row>
-    <row r="49" spans="1:5" ht="49.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="49" spans="1:5" ht="49.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A49" s="4"/>
       <c r="B49" s="8">
         <v>2</v>
@@ -3878,6 +3871,6 @@
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup scale="73" fitToHeight="0" orientation="landscape" r:id="rId1"/>
+  <pageSetup paperSize="9" scale="78" fitToHeight="0" orientation="landscape" r:id="rId1"/>
 </worksheet>
 </file>